--- a/Data Files/9.2. Akun Enquiry - Alias Not Found Or Inactive (U804).xlsx
+++ b/Data Files/9.2. Akun Enquiry - Alias Not Found Or Inactive (U804).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wirafidi/Documents/Komi-API-INCOMING 2/Komi-API-INCOMING 2/Data Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744CFCA2-C101-0044-8E9E-BC2BD824AB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EED591A-7A55-4070-B6A3-982FB469CCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14760" yWindow="920" windowWidth="14480" windowHeight="18040" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
   <sheets>
     <sheet name="PROXY" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>CLRG</t>
   </si>
@@ -36,72 +36,9 @@
     <t>Authorization</t>
   </si>
   <si>
-    <t>requestID</t>
-  </si>
-  <si>
-    <t>requestDate</t>
-  </si>
-  <si>
-    <t>numberOfTrx</t>
-  </si>
-  <si>
-    <t>settlementMethod</t>
-  </si>
-  <si>
-    <t>endToEndID</t>
-  </si>
-  <si>
-    <t>transactionID</t>
-  </si>
-  <si>
-    <t>transactionPurpose</t>
-  </si>
-  <si>
-    <t>settlementAmount</t>
-  </si>
-  <si>
-    <t>settlementCurrency</t>
-  </si>
-  <si>
-    <t>chargeBearer</t>
-  </si>
-  <si>
-    <t>debtorAccountID</t>
-  </si>
-  <si>
-    <t>sendingBank</t>
-  </si>
-  <si>
-    <t>receivingBank</t>
-  </si>
-  <si>
-    <t>20230726APIBANK15100100008108</t>
-  </si>
-  <si>
-    <t>2023-07-26T09:00:55.516</t>
-  </si>
-  <si>
-    <t>20230726APIBANK1510O0100008108</t>
-  </si>
-  <si>
-    <t>20230726APIBANK15100100008188</t>
-  </si>
-  <si>
-    <t>10000.00</t>
-  </si>
-  <si>
     <t>IDR</t>
   </si>
   <si>
-    <t>APIBANK1</t>
-  </si>
-  <si>
-    <t>creditorAccountID</t>
-  </si>
-  <si>
-    <t>APIBANK4</t>
-  </si>
-  <si>
     <t>application/json</t>
   </si>
   <si>
@@ -109,6 +46,111 @@
   </si>
   <si>
     <t>Content_Type</t>
+  </si>
+  <si>
+    <t>AppHdrId</t>
+  </si>
+  <si>
+    <t>ToId</t>
+  </si>
+  <si>
+    <t>BizMsgIdr</t>
+  </si>
+  <si>
+    <t>MsgDefIdr</t>
+  </si>
+  <si>
+    <t>CreDt</t>
+  </si>
+  <si>
+    <t>GrpHdrCreDtTm</t>
+  </si>
+  <si>
+    <t>GrpHdrMsgId</t>
+  </si>
+  <si>
+    <t>GrpHdrNbOfTxs</t>
+  </si>
+  <si>
+    <t>SttlmInfSttlmMtd</t>
+  </si>
+  <si>
+    <t>PmtIdEndToEndId</t>
+  </si>
+  <si>
+    <t>PmtIdTxId</t>
+  </si>
+  <si>
+    <t>PmtIdClrSysRef</t>
+  </si>
+  <si>
+    <t>CtgyPurpPrtry</t>
+  </si>
+  <si>
+    <t>IntrBkSttlmDt</t>
+  </si>
+  <si>
+    <t>ChrgBr</t>
+  </si>
+  <si>
+    <t>FinInstnIdOthrId</t>
+  </si>
+  <si>
+    <t>OthrId</t>
+  </si>
+  <si>
+    <t>CdtrAcctOthrId</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Ccy</t>
+  </si>
+  <si>
+    <t>FASTIDJA</t>
+  </si>
+  <si>
+    <t>BDKIIDJ1</t>
+  </si>
+  <si>
+    <t>20220118FASTIDJA510H9906412065</t>
+  </si>
+  <si>
+    <t>pacs.008.001.08</t>
+  </si>
+  <si>
+    <t>2022-01-18T09:11:43Z</t>
+  </si>
+  <si>
+    <t>2022-01-18T16:08:00.000</t>
+  </si>
+  <si>
+    <t>20220118MEDHIDS1510O0330000016</t>
+  </si>
+  <si>
+    <t>20220118MEDHIDS151003321769</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>51099</t>
+  </si>
+  <si>
+    <t>2021-10-26</t>
+  </si>
+  <si>
+    <t>MEDHIDS1</t>
+  </si>
+  <si>
+    <t>34532.0</t>
+  </si>
+  <si>
+    <t>20220118MEDHIDS151763314330</t>
+  </si>
+  <si>
+    <t>0019845644521100</t>
   </si>
 </sst>
 </file>
@@ -124,7 +166,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -137,8 +179,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -172,16 +220,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -200,9 +264,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -240,7 +304,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -346,7 +410,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -488,7 +552,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -496,112 +560,154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAC831-256C-49B0-B0F6-AAF164E4E88A}">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="10" max="10" width="34.5" customWidth="1"/>
-    <col min="11" max="11" width="38.83203125" customWidth="1"/>
+    <col min="3" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.44140625" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="22.44140625" customWidth="1"/>
+    <col min="9" max="9" width="29.109375" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="31.33203125" customWidth="1"/>
+    <col min="13" max="13" width="28.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="5">
+        <v>1</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2">
-        <v>51001</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2">
-        <v>400000002</v>
       </c>
     </row>
   </sheetData>
